--- a/Lab7/tc.xlsx
+++ b/Lab7/tc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ki2Nam4\Testing\Testing_Lab\Lab7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4887F55-F381-48FD-8AAE-39CE03E76080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0ABEFF6-0065-413F-93CF-3FE7593C3D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1888,7 +1888,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1901,7 +1901,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1911,14 +1911,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1938,6 +1934,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1967,10 +1966,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>24871</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>145256</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>236220</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2000,7 +1999,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="3657600" cy="3679821"/>
+          <a:ext cx="4412456" cy="4442460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3101,14 +3100,14 @@
       </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="B76" s="10" t="s">
+      <c r="B76" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="10"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="19"/>
     </row>
     <row r="77" spans="1:7" ht="43.2">
       <c r="B77" s="4" t="s">
@@ -3417,7 +3416,7 @@
       <c r="C92" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="D92" s="11" t="s">
+      <c r="D92" s="10" t="s">
         <v>186</v>
       </c>
       <c r="E92" s="4" t="s">
@@ -3457,7 +3456,7 @@
       <c r="C94" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D94" s="11" t="s">
+      <c r="D94" s="10" t="s">
         <v>195</v>
       </c>
       <c r="E94" s="4" t="s">
@@ -3471,16 +3470,16 @@
       </c>
     </row>
     <row r="95" spans="2:7">
-      <c r="B95" s="10" t="s">
+      <c r="B95" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="C95" s="10"/>
-      <c r="D95" s="10"/>
-      <c r="E95" s="10"/>
-      <c r="F95" s="10"/>
-      <c r="G95" s="10"/>
-    </row>
-    <row r="96" spans="2:7" ht="28.8">
+      <c r="C95" s="19"/>
+      <c r="D95" s="19"/>
+      <c r="E95" s="19"/>
+      <c r="F95" s="19"/>
+      <c r="G95" s="19"/>
+    </row>
+    <row r="96" spans="2:7">
       <c r="B96" s="4" t="s">
         <v>199</v>
       </c>
@@ -3500,7 +3499,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="2:7" ht="28.8">
+    <row r="97" spans="2:7">
       <c r="B97" s="4" t="s">
         <v>203</v>
       </c>
@@ -3520,7 +3519,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="98" spans="2:7" ht="28.8">
+    <row r="98" spans="2:7">
       <c r="B98" s="4" t="s">
         <v>206</v>
       </c>
@@ -3540,7 +3539,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="99" spans="2:7" ht="28.8">
+    <row r="99" spans="2:7">
       <c r="B99" s="4" t="s">
         <v>209</v>
       </c>
@@ -3560,7 +3559,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="100" spans="2:7" ht="28.8">
+    <row r="100" spans="2:7">
       <c r="B100" s="4" t="s">
         <v>212</v>
       </c>
@@ -3601,14 +3600,14 @@
       </c>
     </row>
     <row r="102" spans="2:7">
-      <c r="B102" s="10" t="s">
+      <c r="B102" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="C102" s="10"/>
-      <c r="D102" s="10"/>
-      <c r="E102" s="10"/>
-      <c r="F102" s="10"/>
-      <c r="G102" s="10"/>
+      <c r="C102" s="19"/>
+      <c r="D102" s="19"/>
+      <c r="E102" s="19"/>
+      <c r="F102" s="19"/>
+      <c r="G102" s="19"/>
     </row>
     <row r="103" spans="2:7">
       <c r="B103" s="4" t="s">
@@ -3731,14 +3730,14 @@
       </c>
     </row>
     <row r="109" spans="2:7">
-      <c r="B109" s="10" t="s">
+      <c r="B109" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="C109" s="10"/>
-      <c r="D109" s="10"/>
-      <c r="E109" s="10"/>
-      <c r="F109" s="10"/>
-      <c r="G109" s="10"/>
+      <c r="C109" s="19"/>
+      <c r="D109" s="19"/>
+      <c r="E109" s="19"/>
+      <c r="F109" s="19"/>
+      <c r="G109" s="19"/>
     </row>
     <row r="110" spans="2:7">
       <c r="B110" s="4" t="s">
@@ -3861,14 +3860,14 @@
       </c>
     </row>
     <row r="116" spans="2:7">
-      <c r="B116" s="10" t="s">
+      <c r="B116" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="C116" s="10"/>
-      <c r="D116" s="10"/>
-      <c r="E116" s="10"/>
-      <c r="F116" s="10"/>
-      <c r="G116" s="10"/>
+      <c r="C116" s="19"/>
+      <c r="D116" s="19"/>
+      <c r="E116" s="19"/>
+      <c r="F116" s="19"/>
+      <c r="G116" s="19"/>
     </row>
     <row r="117" spans="2:7" ht="28.8">
       <c r="B117" s="4" t="s">
@@ -4021,415 +4020,324 @@
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="B2" s="12" t="s">
+      <c r="B2" t="s">
         <v>280</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="O2" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="P2" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="Q2" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="R2" s="17" t="s">
+      <c r="R2" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="S2" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="T2" s="18"/>
+      <c r="T2" s="16"/>
     </row>
     <row r="3" spans="1:20">
-      <c r="B3" s="13"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="K3" s="14" t="s">
+      <c r="B3" s="11"/>
+      <c r="K3" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="O3" s="15" t="s">
+      <c r="O3" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="P3" s="15" t="s">
+      <c r="P3" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="Q3" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="R3" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="S3" s="13" t="s">
         <v>299</v>
       </c>
       <c r="T3" s="7"/>
     </row>
     <row r="4" spans="1:20">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="N4" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="O4" s="15" t="s">
+      <c r="O4" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="P4" s="15" t="s">
+      <c r="P4" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="Q4" s="15" t="s">
+      <c r="Q4" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="R4" s="15" t="s">
+      <c r="R4" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="S4" s="15" t="s">
+      <c r="S4" s="13" t="s">
         <v>299</v>
       </c>
       <c r="T4" s="7"/>
     </row>
     <row r="5" spans="1:20">
-      <c r="B5" s="13"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="K5" s="14" t="s">
+      <c r="B5" s="11"/>
+      <c r="K5" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="N5" s="15" t="s">
+      <c r="N5" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="P5" s="15" t="s">
+      <c r="P5" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="Q5" s="15" t="s">
+      <c r="Q5" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="R5" s="15" t="s">
+      <c r="R5" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="S5" s="15" t="s">
+      <c r="S5" s="13" t="s">
         <v>299</v>
       </c>
       <c r="T5" s="7"/>
     </row>
     <row r="6" spans="1:20">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="N6" s="15" t="s">
+      <c r="N6" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="O6" s="15" t="s">
+      <c r="O6" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="P6" s="15" t="s">
+      <c r="P6" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="Q6" s="15" t="s">
+      <c r="Q6" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="R6" s="15" t="s">
+      <c r="R6" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="S6" s="15" t="s">
+      <c r="S6" s="13" t="s">
         <v>297</v>
       </c>
       <c r="T6" s="7"/>
     </row>
     <row r="7" spans="1:20">
-      <c r="B7" s="13"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
+      <c r="B7" s="11"/>
       <c r="K7" s="4"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
       <c r="T7" s="7"/>
     </row>
     <row r="8" spans="1:20">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
       <c r="T8" s="7"/>
     </row>
     <row r="9" spans="1:20">
-      <c r="B9" s="13"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="K9" s="14" t="s">
+      <c r="B9" s="11"/>
+      <c r="K9" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15" t="s">
+      <c r="L9" s="13"/>
+      <c r="M9" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15" t="s">
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
       <c r="T9" s="7"/>
     </row>
     <row r="10" spans="1:20">
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="K10" s="14" t="s">
+      <c r="K10" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15" t="s">
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15" t="s">
+      <c r="O10" s="13"/>
+      <c r="P10" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
       <c r="T10" s="7"/>
     </row>
     <row r="11" spans="1:20">
-      <c r="B11" s="13"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="K11" s="14" t="s">
+      <c r="B11" s="11"/>
+      <c r="K11" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15" t="s">
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
       <c r="T11" s="7"/>
     </row>
     <row r="12" spans="1:20">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15" t="s">
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="S12" s="15"/>
+      <c r="S12" s="13"/>
       <c r="T12" s="7"/>
     </row>
     <row r="13" spans="1:20">
-      <c r="B13" s="13"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="K13" s="14" t="s">
+      <c r="B13" s="11"/>
+      <c r="K13" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15" t="s">
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13" t="s">
         <v>304</v>
       </c>
       <c r="T13" s="7"/>
     </row>
     <row r="14" spans="1:20">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="57.6">
-      <c r="B17" s="16" t="s">
+    <row r="17" spans="2:9" ht="28.8">
+      <c r="B17" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="I17" s="16" t="s">
+      <c r="I17" s="14" t="s">
         <v>316</v>
       </c>
     </row>
@@ -4446,10 +4354,10 @@
       <c r="E18" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="13">
         <v>100</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="12" t="s">
         <v>321</v>
       </c>
       <c r="H18" s="4"/>
@@ -4468,10 +4376,10 @@
       <c r="E19" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="13">
         <v>100</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="12" t="s">
         <v>325</v>
       </c>
       <c r="H19" s="4"/>
@@ -4490,10 +4398,10 @@
       <c r="E20" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="13">
         <v>100</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="12" t="s">
         <v>327</v>
       </c>
       <c r="H20" s="4"/>
@@ -4512,10 +4420,10 @@
       <c r="E21" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="13">
         <v>100</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="12" t="s">
         <v>325</v>
       </c>
       <c r="H21" s="4"/>
@@ -4534,10 +4442,10 @@
       <c r="E22" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="13">
         <v>100</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="12" t="s">
         <v>327</v>
       </c>
       <c r="H22" s="4"/>
@@ -4556,10 +4464,10 @@
       <c r="E23" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="13">
         <v>100</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="12" t="s">
         <v>332</v>
       </c>
       <c r="H23" s="4"/>
@@ -4578,10 +4486,10 @@
       <c r="E24" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="13">
         <v>100</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="G24" s="12" t="s">
         <v>334</v>
       </c>
       <c r="H24" s="4"/>
@@ -4600,10 +4508,10 @@
       <c r="E25" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="13">
         <v>600</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="12" t="s">
         <v>337</v>
       </c>
       <c r="H25" s="4"/>
@@ -4633,38 +4541,38 @@
       </c>
     </row>
     <row r="2" spans="8:15">
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="17" t="s">
         <v>340</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="O2" s="17" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="3" spans="8:15">
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
     </row>
     <row r="4" spans="8:15">
       <c r="I4" s="3" t="s">
@@ -4943,15 +4851,15 @@
       </c>
     </row>
     <row r="16" spans="8:15">
-      <c r="I16" s="20" t="s">
+      <c r="I16" s="18" t="s">
         <v>404</v>
       </c>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
     </row>
     <row r="17" spans="9:15">
       <c r="I17" s="4" t="s">
